--- a/z0bug_odoo/testenv/account_account.xlsx
+++ b/z0bug_odoo/testenv/account_account.xlsx
@@ -85,6 +85,9 @@
     <t xml:space="preserve">account.data_account_type_receivable</t>
   </si>
   <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
     <t xml:space="preserve">l10n_generic_coa.conf_ova</t>
   </si>
   <si>
@@ -134,9 +137,6 @@
   </si>
   <si>
     <t xml:space="preserve">Effetti attivi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True</t>
   </si>
   <si>
     <t xml:space="preserve">z0bug.coa_liq_tra2</t>
@@ -436,7 +436,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -687,18 +687,18 @@
         <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>101300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>11</v>
@@ -709,67 +709,67 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>10301</v>
+        <v>103010</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>101401</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>101501</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>101600</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -777,13 +777,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>101701</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
@@ -794,19 +794,19 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>101710</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -823,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -840,7 +840,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -891,7 +891,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -925,7 +925,7 @@
         <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -959,7 +959,7 @@
         <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1027,7 +1027,7 @@
         <v>68</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1061,7 +1061,7 @@
         <v>68</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" s="4"/>
     </row>
@@ -1183,7 +1183,7 @@
         <v>80</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1200,7 +1200,7 @@
         <v>80</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -1254,7 +1254,7 @@
         <v>53</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F40" s="4"/>
     </row>
@@ -1272,7 +1272,7 @@
         <v>102</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F41" s="4"/>
     </row>
